--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N49_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N49_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>63.42032005443846</v>
+        <v>10.30580200884625</v>
       </c>
       <c r="D2" t="n">
-        <v>63.6062688314134</v>
+        <v>10.33601868510468</v>
       </c>
       <c r="E2" t="n">
-        <v>17.8597839310262</v>
+        <v>2.902214888791758</v>
       </c>
       <c r="F2" t="n">
-        <v>17.36120914292767</v>
+        <v>2.821196485725747</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.02225715282441</v>
+        <v>9.428616787333967</v>
       </c>
       <c r="D3" t="n">
-        <v>58.35485607590729</v>
+        <v>9.482664112334934</v>
       </c>
       <c r="E3" t="n">
-        <v>17.8597839310262</v>
+        <v>2.902214888791758</v>
       </c>
       <c r="F3" t="n">
-        <v>17.36120914292767</v>
+        <v>2.821196485725747</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.93017890697977</v>
+        <v>6.326154072384213</v>
       </c>
       <c r="D4" t="n">
-        <v>44.28659099664165</v>
+        <v>7.196571036954269</v>
       </c>
       <c r="E4" t="n">
-        <v>17.8597839310262</v>
+        <v>2.902214888791758</v>
       </c>
       <c r="F4" t="n">
-        <v>17.36120914292767</v>
+        <v>2.821196485725747</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>48.97153590979924</v>
+        <v>7.957874585342376</v>
       </c>
       <c r="D5" t="n">
-        <v>49.69103201887798</v>
+        <v>8.074792703067672</v>
       </c>
       <c r="E5" t="n">
-        <v>17.8597839310262</v>
+        <v>2.902214888791758</v>
       </c>
       <c r="F5" t="n">
-        <v>17.36120914292767</v>
+        <v>2.821196485725747</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.19939331270777</v>
+        <v>3.932401413315013</v>
       </c>
       <c r="D6" t="n">
-        <v>23.2842159589829</v>
+        <v>3.783685093334721</v>
       </c>
       <c r="E6" t="n">
-        <v>17.8597839310262</v>
+        <v>2.902214888791758</v>
       </c>
       <c r="F6" t="n">
-        <v>17.36120914292767</v>
+        <v>2.821196485725747</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.47509796386313</v>
+        <v>6.577203419127758</v>
       </c>
       <c r="D7" t="n">
-        <v>39.48947544743422</v>
+        <v>6.41703976020806</v>
       </c>
       <c r="E7" t="n">
-        <v>17.8597839310262</v>
+        <v>2.902214888791758</v>
       </c>
       <c r="F7" t="n">
-        <v>17.36120914292767</v>
+        <v>2.821196485725747</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>75.80691118108446</v>
+        <v>12.31862306692623</v>
       </c>
       <c r="D8" t="n">
-        <v>75.38209640972461</v>
+        <v>12.24959066658025</v>
       </c>
       <c r="E8" t="n">
-        <v>17.8597839310262</v>
+        <v>2.902214888791758</v>
       </c>
       <c r="F8" t="n">
-        <v>17.36120914292767</v>
+        <v>2.821196485725747</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>82.99822149507207</v>
+        <v>13.48721099294921</v>
       </c>
       <c r="D9" t="n">
-        <v>82.04739489217125</v>
+        <v>13.33270166997783</v>
       </c>
       <c r="E9" t="n">
-        <v>17.8597839310262</v>
+        <v>2.902214888791758</v>
       </c>
       <c r="F9" t="n">
-        <v>17.36120914292767</v>
+        <v>2.821196485725747</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>75.58669806633209</v>
+        <v>12.28283843577896</v>
       </c>
       <c r="D10" t="n">
-        <v>74.76341957416881</v>
+        <v>12.14905568080243</v>
       </c>
       <c r="E10" t="n">
-        <v>17.8597839310262</v>
+        <v>2.902214888791758</v>
       </c>
       <c r="F10" t="n">
-        <v>17.36120914292767</v>
+        <v>2.821196485725747</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>62.70777990241796</v>
+        <v>10.19001423414292</v>
       </c>
       <c r="D11" t="n">
-        <v>62.52997975281672</v>
+        <v>10.16112170983272</v>
       </c>
       <c r="E11" t="n">
-        <v>17.8597839310262</v>
+        <v>2.902214888791758</v>
       </c>
       <c r="F11" t="n">
-        <v>17.36120914292767</v>
+        <v>2.821196485725747</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
